--- a/public/jadwal guru hari.xlsx
+++ b/public/jadwal guru hari.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\absensismkn8\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C788E3F-4CE7-4D45-B415-DB181590C7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573E957C-F69F-4C21-AEB8-D9D4F63CEA38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{0462380C-0169-499F-940D-9E794747BCCB}"/>
   </bookViews>
@@ -2380,6 +2380,7 @@
   <dimension ref="A1:CA120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="7" max="7" width="63.85546875" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
